--- a/artfynd/A 2892-2026 artfynd.xlsx
+++ b/artfynd/A 2892-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129423638</v>
       </c>
       <c r="B2" t="n">
-        <v>91620</v>
+        <v>91795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,6 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
@@ -750,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>Enstaka fruktkroppar I hällmarkstallskog &gt;150 år gammal med rikliga spridda förekomster</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2892-2026 artfynd.xlsx
+++ b/artfynd/A 2892-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129423638</v>
       </c>
       <c r="B2" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2892-2026 artfynd.xlsx
+++ b/artfynd/A 2892-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129423638</v>
       </c>
       <c r="B2" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2892-2026 artfynd.xlsx
+++ b/artfynd/A 2892-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129423638</v>
       </c>
       <c r="B2" t="n">
-        <v>91797</v>
+        <v>91805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
